--- a/Excel/Vertical/perbandingan_Jumlah Simpul.xlsx
+++ b/Excel/Vertical/perbandingan_Jumlah Simpul.xlsx
@@ -450,10 +450,10 @@
         <v>3</v>
       </c>
       <c r="E2">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F2">
-        <v>0.5795454545454546</v>
+        <v>0.7045454545454546</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -473,10 +473,10 @@
         <v>3</v>
       </c>
       <c r="E3">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F3">
-        <v>0.8296529968454258</v>
+        <v>0.8769716088328076</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -496,10 +496,10 @@
         <v>3</v>
       </c>
       <c r="E4">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F4">
-        <v>0.9512619669277633</v>
+        <v>0.9651871192341166</v>
       </c>
       <c r="G4" t="s">
         <v>12</v>
@@ -519,10 +519,10 @@
         <v>3</v>
       </c>
       <c r="E5">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="F5">
-        <v>0.986920605782469</v>
+        <v>0.9910509407985314</v>
       </c>
       <c r="G5" t="s">
         <v>12</v>
@@ -542,10 +542,10 @@
         <v>8</v>
       </c>
       <c r="E6">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>0.6043956043956044</v>
+        <v>0.6483516483516484</v>
       </c>
       <c r="G6" t="s">
         <v>12</v>
@@ -565,10 +565,10 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F7">
-        <v>0.7975077881619937</v>
+        <v>0.8566978193146417</v>
       </c>
       <c r="G7" t="s">
         <v>12</v>
@@ -588,10 +588,10 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F8">
-        <v>0.948203842940685</v>
+        <v>0.9632414369256475</v>
       </c>
       <c r="G8" t="s">
         <v>12</v>
@@ -611,10 +611,10 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F9">
-        <v>0.9867109634551495</v>
+        <v>0.9889258028792912</v>
       </c>
       <c r="G9" t="s">
         <v>12</v>
@@ -634,10 +634,10 @@
         <v>9</v>
       </c>
       <c r="E10">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>0.5277777777777778</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="G10" t="s">
         <v>12</v>
@@ -657,10 +657,10 @@
         <v>9</v>
       </c>
       <c r="E11">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="F11">
-        <v>0.7881944444444444</v>
+        <v>0.8402777777777778</v>
       </c>
       <c r="G11" t="s">
         <v>12</v>
@@ -680,10 +680,10 @@
         <v>9</v>
       </c>
       <c r="E12">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F12">
-        <v>0.9510869565217391</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="G12" t="s">
         <v>12</v>
@@ -703,10 +703,10 @@
         <v>9</v>
       </c>
       <c r="E13">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F13">
-        <v>0.9870967741935484</v>
+        <v>0.9887694145758662</v>
       </c>
       <c r="G13" t="s">
         <v>12</v>
@@ -726,10 +726,10 @@
         <v>10</v>
       </c>
       <c r="E14">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="F14">
-        <v>0.5865384615384616</v>
+        <v>0.7211538461538461</v>
       </c>
       <c r="G14" t="s">
         <v>12</v>
@@ -749,10 +749,10 @@
         <v>10</v>
       </c>
       <c r="E15">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="F15">
-        <v>0.8461538461538461</v>
+        <v>0.8897435897435897</v>
       </c>
       <c r="G15" t="s">
         <v>12</v>
@@ -772,10 +772,10 @@
         <v>10</v>
       </c>
       <c r="E16">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F16">
-        <v>0.9602911978821972</v>
+        <v>0.972203838517538</v>
       </c>
       <c r="G16" t="s">
         <v>12</v>
@@ -795,10 +795,10 @@
         <v>10</v>
       </c>
       <c r="E17">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="F17">
-        <v>0.9893300682175966</v>
+        <v>0.9926534895924436</v>
       </c>
       <c r="G17" t="s">
         <v>12</v>
@@ -818,10 +818,10 @@
         <v>11</v>
       </c>
       <c r="E18">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F18">
-        <v>0.8133333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="G18" t="s">
         <v>12</v>
@@ -841,10 +841,10 @@
         <v>11</v>
       </c>
       <c r="E19">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F19">
-        <v>0.9215328467153284</v>
+        <v>0.9543795620437956</v>
       </c>
       <c r="G19" t="s">
         <v>12</v>
@@ -864,10 +864,10 @@
         <v>11</v>
       </c>
       <c r="E20">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F20">
-        <v>0.9758698092031426</v>
+        <v>0.9859708193041526</v>
       </c>
       <c r="G20" t="s">
         <v>12</v>
@@ -887,10 +887,10 @@
         <v>11</v>
       </c>
       <c r="E21">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F21">
-        <v>0.9930454471939189</v>
+        <v>0.9959566553453016</v>
       </c>
       <c r="G21" t="s">
         <v>12</v>

--- a/Excel/Vertical/perbandingan_Jumlah Simpul.xlsx
+++ b/Excel/Vertical/perbandingan_Jumlah Simpul.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="15">
   <si>
     <t>Kombinasi</t>
   </si>
@@ -22,7 +22,7 @@
     <t>Ukuran</t>
   </si>
   <si>
-    <t>Nilai</t>
+    <t>value</t>
   </si>
   <si>
     <t>Map</t>
@@ -53,6 +53,12 @@
   </si>
   <si>
     <t>Tetap</t>
+  </si>
+  <si>
+    <t>Naik</t>
+  </si>
+  <si>
+    <t>Turun</t>
   </si>
 </sst>
 </file>
@@ -449,6 +455,12 @@
       <c r="D2" t="s">
         <v>3</v>
       </c>
+      <c r="E2">
+        <v>88</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
       <c r="G2" t="s">
         <v>12</v>
       </c>
@@ -466,6 +478,12 @@
       <c r="D3" t="s">
         <v>3</v>
       </c>
+      <c r="E3">
+        <v>317</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
       <c r="G3" t="s">
         <v>12</v>
       </c>
@@ -483,6 +501,12 @@
       <c r="D4" t="s">
         <v>3</v>
       </c>
+      <c r="E4">
+        <v>1149</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
       <c r="G4" t="s">
         <v>12</v>
       </c>
@@ -500,6 +524,12 @@
       <c r="D5" t="s">
         <v>3</v>
       </c>
+      <c r="E5">
+        <v>4358</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
       <c r="G5" t="s">
         <v>12</v>
       </c>
@@ -517,8 +547,14 @@
       <c r="D6" t="s">
         <v>8</v>
       </c>
+      <c r="E6">
+        <v>60</v>
+      </c>
+      <c r="F6">
+        <v>0.3406593406593407</v>
+      </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -534,8 +570,14 @@
       <c r="D7" t="s">
         <v>8</v>
       </c>
+      <c r="E7">
+        <v>148</v>
+      </c>
+      <c r="F7">
+        <v>0.5389408099688473</v>
+      </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -551,8 +593,14 @@
       <c r="D8" t="s">
         <v>8</v>
       </c>
+      <c r="E8">
+        <v>406</v>
+      </c>
+      <c r="F8">
+        <v>0.6608187134502924</v>
+      </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -568,8 +616,14 @@
       <c r="D9" t="s">
         <v>8</v>
       </c>
+      <c r="E9">
+        <v>1230</v>
+      </c>
+      <c r="F9">
+        <v>0.7275747508305648</v>
+      </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -585,8 +639,14 @@
       <c r="D10" t="s">
         <v>9</v>
       </c>
+      <c r="E10">
+        <v>77</v>
+      </c>
+      <c r="F10">
+        <v>-0.06944444444444445</v>
+      </c>
       <c r="G10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -602,8 +662,14 @@
       <c r="D11" t="s">
         <v>9</v>
       </c>
+      <c r="E11">
+        <v>259</v>
+      </c>
+      <c r="F11">
+        <v>0.1006944444444444</v>
+      </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -619,8 +685,14 @@
       <c r="D12" t="s">
         <v>9</v>
       </c>
+      <c r="E12">
+        <v>841</v>
+      </c>
+      <c r="F12">
+        <v>0.2382246376811594</v>
+      </c>
       <c r="G12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -636,8 +708,14 @@
       <c r="D13" t="s">
         <v>9</v>
       </c>
+      <c r="E13">
+        <v>2765</v>
+      </c>
+      <c r="F13">
+        <v>0.3393070489844683</v>
+      </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -653,8 +731,14 @@
       <c r="D14" t="s">
         <v>10</v>
       </c>
+      <c r="E14">
+        <v>37</v>
+      </c>
+      <c r="F14">
+        <v>0.6442307692307693</v>
+      </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -670,8 +754,14 @@
       <c r="D15" t="s">
         <v>10</v>
       </c>
+      <c r="E15">
+        <v>52</v>
+      </c>
+      <c r="F15">
+        <v>0.8666666666666667</v>
+      </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -687,8 +777,14 @@
       <c r="D16" t="s">
         <v>10</v>
       </c>
+      <c r="E16">
+        <v>54</v>
+      </c>
+      <c r="F16">
+        <v>0.9642620780939775</v>
+      </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -704,8 +800,14 @@
       <c r="D17" t="s">
         <v>10</v>
       </c>
+      <c r="E17">
+        <v>59</v>
+      </c>
+      <c r="F17">
+        <v>0.9896799020465279</v>
+      </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -721,8 +823,14 @@
       <c r="D18" t="s">
         <v>11</v>
       </c>
+      <c r="E18">
+        <v>88</v>
+      </c>
+      <c r="F18">
+        <v>0.4133333333333333</v>
+      </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -738,8 +846,14 @@
       <c r="D19" t="s">
         <v>11</v>
       </c>
+      <c r="E19">
+        <v>317</v>
+      </c>
+      <c r="F19">
+        <v>0.4215328467153285</v>
+      </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -755,8 +869,14 @@
       <c r="D20" t="s">
         <v>11</v>
       </c>
+      <c r="E20">
+        <v>1149</v>
+      </c>
+      <c r="F20">
+        <v>0.3552188552188552</v>
+      </c>
       <c r="G20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -772,8 +892,14 @@
       <c r="D21" t="s">
         <v>11</v>
       </c>
+      <c r="E21">
+        <v>4358</v>
+      </c>
+      <c r="F21">
+        <v>0.2951641597929808</v>
+      </c>
       <c r="G21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Vertical/perbandingan_Jumlah Simpul.xlsx
+++ b/Excel/Vertical/perbandingan_Jumlah Simpul.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Vertical\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3536A7F2-6881-492E-9374-5FE0E955EB88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -64,8 +70,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,13 +134,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -172,7 +186,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -206,6 +220,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -240,9 +255,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -415,11 +431,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="9.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -442,7 +461,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -465,7 +484,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -488,7 +507,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -511,7 +530,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -534,7 +553,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -551,13 +570,13 @@
         <v>60</v>
       </c>
       <c r="F6">
-        <v>0.3406593406593407</v>
+        <v>0.34065934065934073</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -571,16 +590,16 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F7">
-        <v>0.5389408099688473</v>
+        <v>0.54828660436137067</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -594,16 +613,16 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>406</v>
+        <v>307</v>
       </c>
       <c r="F8">
-        <v>0.6608187134502924</v>
+        <v>0.74352548036758559</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -617,16 +636,16 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>1230</v>
+        <v>656</v>
       </c>
       <c r="F9">
-        <v>0.7275747508305648</v>
+        <v>0.85470653377630124</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -643,13 +662,13 @@
         <v>77</v>
       </c>
       <c r="F10">
-        <v>-0.06944444444444445</v>
+        <v>-6.9444444444444448E-2</v>
       </c>
       <c r="G10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -666,13 +685,13 @@
         <v>259</v>
       </c>
       <c r="F11">
-        <v>0.1006944444444444</v>
+        <v>0.10069444444444441</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -695,7 +714,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -712,13 +731,13 @@
         <v>2765</v>
       </c>
       <c r="F13">
-        <v>0.3393070489844683</v>
+        <v>0.33930704898446828</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -735,13 +754,13 @@
         <v>37</v>
       </c>
       <c r="F14">
-        <v>0.6442307692307693</v>
+        <v>0.64423076923076927</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -764,7 +783,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -781,13 +800,13 @@
         <v>54</v>
       </c>
       <c r="F16">
-        <v>0.9642620780939775</v>
+        <v>0.96426207809397746</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -804,13 +823,13 @@
         <v>59</v>
       </c>
       <c r="F17">
-        <v>0.9896799020465279</v>
+        <v>0.98967990204652789</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -827,13 +846,13 @@
         <v>88</v>
       </c>
       <c r="F18">
-        <v>0.4133333333333333</v>
+        <v>0.41333333333333327</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -850,13 +869,13 @@
         <v>317</v>
       </c>
       <c r="F19">
-        <v>0.4215328467153285</v>
+        <v>0.42153284671532848</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -873,13 +892,13 @@
         <v>1149</v>
       </c>
       <c r="F20">
-        <v>0.3552188552188552</v>
+        <v>0.35521885521885521</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -896,7 +915,7 @@
         <v>4358</v>
       </c>
       <c r="F21">
-        <v>0.2951641597929808</v>
+        <v>0.29516415979298077</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
